--- a/output/Data and Chart Outputs/egypt_grid_load_daily.xlsx
+++ b/output/Data and Chart Outputs/egypt_grid_load_daily.xlsx
@@ -20,8 +20,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -61,12 +61,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -699,7 +700,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -714,7 +714,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -729,7 +728,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -789,7 +787,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>46305</v>
       </c>
       <c r="B2" t="n">
@@ -805,7 +803,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>46306</v>
       </c>
       <c r="D3" t="n">

--- a/output/Data and Chart Outputs/egypt_grid_load_daily.xlsx
+++ b/output/Data and Chart Outputs/egypt_grid_load_daily.xlsx
@@ -20,8 +20,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -61,13 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -193,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$3</f>
+              <f>'Chart'!$E$2:$E$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$3</f>
+              <f>'Chart'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -229,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$3</f>
+              <f>'Chart'!$E$2:$E$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$3</f>
+              <f>'Chart'!$C$2:$C$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -265,12 +264,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$3</f>
+              <f>'Chart'!$E$2:$E$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$3</f>
+              <f>'Chart'!$D$2:$D$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -700,6 +699,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -714,6 +714,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -728,6 +729,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -753,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -787,7 +789,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>46305</v>
       </c>
       <c r="B2" t="n">
@@ -803,11 +805,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>46306</v>
       </c>
       <c r="D3" t="n">
         <v>33100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B4" t="n">
+        <v>32400</v>
+      </c>
+      <c r="C4" t="n">
+        <v>23463</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="D5" t="n">
+        <v>32500</v>
       </c>
     </row>
   </sheetData>
@@ -822,7 +843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -894,6 +915,38 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B4" t="n">
+        <v>32400</v>
+      </c>
+      <c r="C4" t="n">
+        <v>23463</v>
+      </c>
+      <c r="D4" t="n">
+        <v>29</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="E5" t="n">
+        <v>32500</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/egypt_grid_load_daily.xlsx
+++ b/output/Data and Chart Outputs/egypt_grid_load_daily.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$5</f>
+              <f>'Chart'!$E$2:$E$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$5</f>
+              <f>'Chart'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$5</f>
+              <f>'Chart'!$E$2:$E$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$5</f>
+              <f>'Chart'!$C$2:$C$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -264,12 +264,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$5</f>
+              <f>'Chart'!$E$2:$E$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$5</f>
+              <f>'Chart'!$D$2:$D$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -755,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -827,7 +827,21 @@
       <c r="A5" s="3" t="n">
         <v>46322</v>
       </c>
+      <c r="B5" t="n">
+        <v>32400</v>
+      </c>
+      <c r="C5" t="n">
+        <v>22878</v>
+      </c>
       <c r="D5" t="n">
+        <v>32500</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="D6" t="n">
         <v>32500</v>
       </c>
     </row>
@@ -843,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -938,12 +952,39 @@
       <c r="A5" s="4" t="n">
         <v>46322</v>
       </c>
+      <c r="B5" t="n">
+        <v>32400</v>
+      </c>
+      <c r="C5" t="n">
+        <v>22878</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
       <c r="E5" t="n">
         <v>32500</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="E6" t="n">
+        <v>32500</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/egypt_grid_load_daily.xlsx
+++ b/output/Data and Chart Outputs/egypt_grid_load_daily.xlsx
@@ -20,8 +20,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -61,12 +61,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -699,7 +700,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -714,7 +714,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -729,7 +728,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -789,7 +787,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>46305</v>
       </c>
       <c r="B2" t="n">
@@ -805,7 +803,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>46306</v>
       </c>
       <c r="D3" t="n">
@@ -813,7 +811,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>46321</v>
       </c>
       <c r="B4" t="n">
@@ -824,7 +822,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>46322</v>
       </c>
       <c r="B5" t="n">
@@ -838,7 +836,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>46323</v>
       </c>
       <c r="D6" t="n">

--- a/output/Data and Chart Outputs/egypt_grid_load_daily.xlsx
+++ b/output/Data and Chart Outputs/egypt_grid_load_daily.xlsx
@@ -20,8 +20,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -61,13 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -193,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$6</f>
+              <f>'Chart'!$E$2:$E$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$6</f>
+              <f>'Chart'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -229,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$6</f>
+              <f>'Chart'!$E$2:$E$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$6</f>
+              <f>'Chart'!$C$2:$C$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -265,12 +264,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$6</f>
+              <f>'Chart'!$E$2:$E$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$6</f>
+              <f>'Chart'!$D$2:$D$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -700,6 +699,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -714,6 +714,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -728,6 +729,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -753,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -787,7 +789,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>46305</v>
       </c>
       <c r="B2" t="n">
@@ -803,7 +805,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>46306</v>
       </c>
       <c r="D3" t="n">
@@ -811,7 +813,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>46321</v>
       </c>
       <c r="B4" t="n">
@@ -822,7 +824,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>46322</v>
       </c>
       <c r="B5" t="n">
@@ -836,10 +838,24 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>46323</v>
       </c>
+      <c r="B6" t="n">
+        <v>32700</v>
+      </c>
+      <c r="C6" t="n">
+        <v>22799</v>
+      </c>
       <c r="D6" t="n">
+        <v>32500</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="D7" t="n">
         <v>32500</v>
       </c>
     </row>
@@ -855,7 +871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -977,12 +993,39 @@
       <c r="A6" s="4" t="n">
         <v>46323</v>
       </c>
+      <c r="B6" t="n">
+        <v>32700</v>
+      </c>
+      <c r="C6" t="n">
+        <v>22799</v>
+      </c>
+      <c r="D6" t="n">
+        <v>29</v>
+      </c>
       <c r="E6" t="n">
         <v>32500</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="E7" t="n">
+        <v>32500</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/egypt_grid_load_daily.xlsx
+++ b/output/Data and Chart Outputs/egypt_grid_load_daily.xlsx
@@ -20,8 +20,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -61,12 +61,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -699,7 +700,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -714,7 +714,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -729,7 +728,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -789,7 +787,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>46305</v>
       </c>
       <c r="B2" t="n">
@@ -805,7 +803,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>46306</v>
       </c>
       <c r="D3" t="n">
@@ -813,7 +811,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>46321</v>
       </c>
       <c r="B4" t="n">
@@ -824,7 +822,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>46322</v>
       </c>
       <c r="B5" t="n">
@@ -838,7 +836,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>46323</v>
       </c>
       <c r="B6" t="n">
@@ -852,7 +850,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>46324</v>
       </c>
       <c r="D7" t="n">
